--- a/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,7 +587,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,7 +634,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -706,7 +681,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -758,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,7 +775,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,7 +822,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -914,7 +869,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -966,7 +916,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1018,7 +963,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1070,7 +1010,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1107,11 +1047,6 @@
       </c>
       <c r="K13" t="n">
         <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/Mantenimiento/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>SOL NACIENTE</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.07921</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.04397</v>
-      </c>
-      <c r="I2" t="n">
-        <v>360</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.07921</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.04397</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>CARLOS MANUEL COX ROSSE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.067909999999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.05753</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1241</v>
-      </c>
-      <c r="J3" t="n">
-        <v>58</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.06791</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.05753</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>80038 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.06649</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.04855999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1292</v>
-      </c>
-      <c r="J4" t="n">
-        <v>59</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.06649</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.04856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>80039 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.07985</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.04161000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>444</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.07985</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.04161</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>80040 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.08074</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.04684</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J6" t="n">
-        <v>63</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.08074</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.04684</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>80041 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.082789999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.0369</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J7" t="n">
-        <v>42</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.08279</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.0369</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>80821 CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.083930000000002</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.03413999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1765</v>
-      </c>
-      <c r="J8" t="n">
-        <v>88</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.083930000000002</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.03414</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>80822 SANTA MARIA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.067399999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.05419999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2138</v>
-      </c>
-      <c r="J9" t="n">
-        <v>86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.0674</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.0542</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -884,28 +952,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>254030</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81608 SAN JOSE</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>-8.0608</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.0551</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1801</v>
-      </c>
-      <c r="J10" t="n">
-        <v>68</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+          <t>81751 DIOS ES AMOR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.05656</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.0531</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -931,28 +1009,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>254030</t>
+          <t>254266</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>81751 DIOS ES AMOR</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>-8.056559999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.0531</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1478</v>
-      </c>
-      <c r="J11" t="n">
-        <v>57</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+          <t>DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.07479208879985</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.0506266257255</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -978,75 +1066,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>658615</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-8.07479208879985</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.0506266257255</v>
-      </c>
-      <c r="I12" t="n">
-        <v>329</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>130105</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LA ESPERANZA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>658615</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>81749 DIVINO JESUS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.069089999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.07153</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J13" t="n">
-        <v>62</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.06909</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.07153</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
